--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_1/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_1/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -1522,7 +1522,7 @@
     <t>0.9983,0.0019,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.9607,0.0979,0.0014,0.0000</t>
+    <t>0.9607,0.0980,0.0014,0.0000</t>
   </si>
   <si>
     <t>0.9944,0.0189,0.0003,0.0000</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_1/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_1/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="527">
   <si>
     <t>Filename</t>
   </si>
@@ -814,25 +814,34 @@
     <t>0,1,0,0</t>
   </si>
   <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,0,1,0</t>
   </si>
   <si>
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,0,0,1</t>
   </si>
   <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0.9971,0.0032,0.0004,0.0000</t>
   </si>
   <si>
-    <t>0.9753,0.0079,0.0008,0.0008</t>
+    <t>0.9753,0.0078,0.0008,0.0008</t>
   </si>
   <si>
     <t>0.9976,0.0019,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.9903,0.0161,0.0011,0.0001</t>
+    <t>0.9903,0.0160,0.0011,0.0001</t>
   </si>
   <si>
     <t>0.9968,0.0070,0.0003,0.0000</t>
@@ -841,10 +850,10 @@
     <t>0.9942,0.0128,0.0004,0.0000</t>
   </si>
   <si>
-    <t>0.9947,0.0102,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9838,0.0342,0.0015,0.0000</t>
+    <t>0.9947,0.0102,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9839,0.0341,0.0015,0.0000</t>
   </si>
   <si>
     <t>0.9965,0.0112,0.0002,0.0000</t>
@@ -853,7 +862,7 @@
     <t>0.9960,0.0109,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.9762,0.0573,0.0013,0.0000</t>
+    <t>0.9762,0.0572,0.0013,0.0000</t>
   </si>
   <si>
     <t>0.9969,0.0064,0.0003,0.0000</t>
@@ -862,28 +871,28 @@
     <t>0.9940,0.0047,0.0011,0.0000</t>
   </si>
   <si>
-    <t>0.9251,0.0482,0.0121,0.0000</t>
-  </si>
-  <si>
-    <t>0.9819,0.0012,0.0090,0.0000</t>
-  </si>
-  <si>
-    <t>0.9107,0.0068,0.0556,0.0000</t>
+    <t>0.9252,0.0480,0.0121,0.0000</t>
+  </si>
+  <si>
+    <t>0.9819,0.0012,0.0091,0.0000</t>
+  </si>
+  <si>
+    <t>0.9107,0.0068,0.0557,0.0000</t>
   </si>
   <si>
     <t>0.9972,0.0011,0.0007,0.0000</t>
   </si>
   <si>
-    <t>0.0563,0.9847,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.2659,0.9317,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.7808,0.5422,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.4208,0.8685,0.0012,0.0000</t>
+    <t>0.0564,0.9847,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.2664,0.9315,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.7812,0.5415,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.4212,0.8682,0.0012,0.0000</t>
   </si>
   <si>
     <t>0.0164,0.9944,0.0041,0.0000</t>
@@ -895,31 +904,31 @@
     <t>0.9519,0.0093,0.0175,0.0000</t>
   </si>
   <si>
-    <t>0.9393,0.0005,0.0615,0.0000</t>
-  </si>
-  <si>
-    <t>0.8939,0.0042,0.0726,0.0000</t>
-  </si>
-  <si>
-    <t>0.9486,0.0035,0.0283,0.0000</t>
-  </si>
-  <si>
-    <t>0.8347,0.0003,0.2506,0.0000</t>
-  </si>
-  <si>
-    <t>0.3213,0.0001,0.8380,0.0001</t>
+    <t>0.9393,0.0005,0.0616,0.0000</t>
+  </si>
+  <si>
+    <t>0.8938,0.0042,0.0727,0.0000</t>
+  </si>
+  <si>
+    <t>0.9485,0.0035,0.0284,0.0000</t>
+  </si>
+  <si>
+    <t>0.8345,0.0003,0.2511,0.0000</t>
+  </si>
+  <si>
+    <t>0.3209,0.0001,0.8383,0.0001</t>
   </si>
   <si>
     <t>0.9945,0.0128,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.9823,0.0511,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.6760,0.0015,0.3264,0.0001</t>
-  </si>
-  <si>
-    <t>0.8057,0.1999,0.0135,0.0001</t>
+    <t>0.9823,0.0510,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.6756,0.0015,0.3270,0.0001</t>
+  </si>
+  <si>
+    <t>0.8059,0.1995,0.0135,0.0001</t>
   </si>
   <si>
     <t>0.9913,0.0102,0.0019,0.0000</t>
@@ -928,100 +937,100 @@
     <t>0.9900,0.0192,0.0013,0.0000</t>
   </si>
   <si>
-    <t>0.9735,0.0866,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9109,0.2145,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0032,0.9617,0.7282,0.0001</t>
-  </si>
-  <si>
-    <t>0.0448,0.0044,0.9632,0.0005</t>
-  </si>
-  <si>
-    <t>0.4126,0.0112,0.7315,0.0002</t>
+    <t>0.9735,0.0864,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9110,0.2142,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0032,0.9616,0.7288,0.0001</t>
+  </si>
+  <si>
+    <t>0.0448,0.0043,0.9633,0.0005</t>
+  </si>
+  <si>
+    <t>0.4124,0.0111,0.7318,0.0002</t>
   </si>
   <si>
     <t>0.9467,0.0027,0.0196,0.0001</t>
   </si>
   <si>
-    <t>0.0102,0.9268,0.6602,0.0003</t>
+    <t>0.0102,0.9266,0.6607,0.0003</t>
   </si>
   <si>
     <t>0.0011,0.9972,0.0139,0.0006</t>
   </si>
   <si>
-    <t>0.0699,0.0367,0.9453,0.0009</t>
-  </si>
-  <si>
-    <t>0.8724,0.1079,0.0008,0.0012</t>
-  </si>
-  <si>
-    <t>0.0005,0.9997,0.0058,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9995,0.0918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0500,0.0000</t>
-  </si>
-  <si>
-    <t>0.0086,0.1357,0.9792,0.0005</t>
-  </si>
-  <si>
-    <t>0.0171,0.3390,0.9496,0.0004</t>
-  </si>
-  <si>
-    <t>0.4878,0.0018,0.6278,0.0001</t>
-  </si>
-  <si>
-    <t>0.9618,0.0002,0.0439,0.0000</t>
-  </si>
-  <si>
-    <t>0.7769,0.0013,0.2738,0.0000</t>
-  </si>
-  <si>
-    <t>0.5419,0.0112,0.4470,0.0002</t>
-  </si>
-  <si>
-    <t>0.9936,0.0150,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9875,0.0227,0.0014,0.0000</t>
+    <t>0.0698,0.0366,0.9454,0.0009</t>
+  </si>
+  <si>
+    <t>0.8726,0.1077,0.0008,0.0012</t>
+  </si>
+  <si>
+    <t>0.0005,0.9997,0.0059,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9995,0.0919,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0501,0.0000</t>
+  </si>
+  <si>
+    <t>0.0086,0.1349,0.9792,0.0005</t>
+  </si>
+  <si>
+    <t>0.0171,0.3381,0.9497,0.0004</t>
+  </si>
+  <si>
+    <t>0.4874,0.0018,0.6284,0.0001</t>
+  </si>
+  <si>
+    <t>0.9618,0.0002,0.0441,0.0000</t>
+  </si>
+  <si>
+    <t>0.7768,0.0013,0.2742,0.0000</t>
+  </si>
+  <si>
+    <t>0.5417,0.0112,0.4476,0.0002</t>
+  </si>
+  <si>
+    <t>0.9936,0.0149,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9875,0.0226,0.0014,0.0000</t>
   </si>
   <si>
     <t>0.9978,0.0050,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.9607,0.0244,0.0080,0.0000</t>
-  </si>
-  <si>
-    <t>0.9907,0.0171,0.0012,0.0000</t>
+    <t>0.9608,0.0243,0.0080,0.0000</t>
+  </si>
+  <si>
+    <t>0.9907,0.0170,0.0012,0.0000</t>
   </si>
   <si>
     <t>0.9960,0.0077,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.9913,0.0171,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9985,0.7721,0.0000</t>
-  </si>
-  <si>
-    <t>0.0056,0.0528,0.9942,0.0000</t>
-  </si>
-  <si>
-    <t>0.0427,0.0331,0.9714,0.0006</t>
-  </si>
-  <si>
-    <t>0.0012,0.9832,0.8164,0.0001</t>
+    <t>0.9913,0.0170,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9984,0.7724,0.0000</t>
+  </si>
+  <si>
+    <t>0.0056,0.0526,0.9942,0.0000</t>
+  </si>
+  <si>
+    <t>0.0427,0.0330,0.9715,0.0006</t>
+  </si>
+  <si>
+    <t>0.0012,0.9832,0.8165,0.0001</t>
   </si>
   <si>
     <t>0.0027,0.0010,0.9974,0.0001</t>
   </si>
   <si>
-    <t>0.0434,0.9826,0.0066,0.0000</t>
+    <t>0.0435,0.9825,0.0066,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0015,0.0000</t>
@@ -1033,25 +1042,25 @@
     <t>0.9901,0.0137,0.0019,0.0000</t>
   </si>
   <si>
-    <t>0.9572,0.0069,0.0184,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.9658,0.9097,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9238,0.9610,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,0.5164,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9926,0.8754,0.0000</t>
-  </si>
-  <si>
-    <t>0.9418,0.0008,0.0002,0.0073</t>
-  </si>
-  <si>
-    <t>0.6865,0.0237,0.0012,0.0469</t>
+    <t>0.9573,0.0069,0.0184,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9657,0.9098,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9236,0.9611,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9996,0.5169,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9926,0.8755,0.0000</t>
+  </si>
+  <si>
+    <t>0.9417,0.0008,0.0002,0.0073</t>
+  </si>
+  <si>
+    <t>0.6867,0.0236,0.0012,0.0470</t>
   </si>
   <si>
     <t>0.8862,0.0016,0.0005,0.0350</t>
@@ -1063,46 +1072,46 @@
     <t>0.9536,0.0056,0.0005,0.0025</t>
   </si>
   <si>
-    <t>0.4632,0.0232,0.0013,0.1643</t>
-  </si>
-  <si>
-    <t>0.0003,0.9970,0.7495,0.0000</t>
-  </si>
-  <si>
-    <t>0.0034,0.8656,0.9482,0.0001</t>
-  </si>
-  <si>
-    <t>0.0157,0.8654,0.7186,0.0003</t>
-  </si>
-  <si>
-    <t>0.0024,0.9172,0.9389,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9971,0.9219,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9965,0.2685,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0073,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9878,0.0302,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9897,0.0339,0.0004,0.0000</t>
+    <t>0.4634,0.0231,0.0013,0.1646</t>
+  </si>
+  <si>
+    <t>0.0003,0.9970,0.7499,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.8653,0.9483,0.0001</t>
+  </si>
+  <si>
+    <t>0.0157,0.8649,0.7191,0.0003</t>
+  </si>
+  <si>
+    <t>0.0024,0.9171,0.9389,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9971,0.9220,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.9965,0.2689,0.0000</t>
+  </si>
+  <si>
+    <t>0.9973,0.0073,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9878,0.0301,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9897,0.0338,0.0004,0.0000</t>
   </si>
   <si>
     <t>0.9937,0.0183,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.9843,0.0334,0.0011,0.0000</t>
+    <t>0.9843,0.0333,0.0011,0.0000</t>
   </si>
   <si>
     <t>0.9953,0.0111,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.9934,0.0106,0.0008,0.0000</t>
+    <t>0.9934,0.0105,0.0008,0.0000</t>
   </si>
   <si>
     <t>0.9954,0.0087,0.0006,0.0000</t>
@@ -1132,7 +1141,7 @@
     <t>0.9937,0.0122,0.0008,0.0000</t>
   </si>
   <si>
-    <t>0.1841,0.0001,0.9171,0.0000</t>
+    <t>0.1839,0.0001,0.9172,0.0000</t>
   </si>
   <si>
     <t>0.9647,0.0074,0.0120,0.0000</t>
@@ -1141,34 +1150,34 @@
     <t>0.9971,0.0005,0.0010,0.0000</t>
   </si>
   <si>
-    <t>0.9105,0.0035,0.0536,0.0000</t>
-  </si>
-  <si>
-    <t>0.0190,0.9935,0.0029,0.0000</t>
+    <t>0.9104,0.0035,0.0536,0.0000</t>
+  </si>
+  <si>
+    <t>0.0191,0.9935,0.0029,0.0000</t>
   </si>
   <si>
     <t>0.0239,0.9943,0.0012,0.0000</t>
   </si>
   <si>
-    <t>0.7578,0.6993,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.7738,0.6247,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0253,0.9922,0.0028,0.0000</t>
+    <t>0.7582,0.6987,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7742,0.6239,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0254,0.9922,0.0028,0.0000</t>
   </si>
   <si>
     <t>0.0006,0.9998,0.0009,0.0000</t>
   </si>
   <si>
-    <t>0.9905,0.0314,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9597,0.0607,0.0034,0.0000</t>
-  </si>
-  <si>
-    <t>0.9447,0.0033,0.0356,0.0000</t>
+    <t>0.9906,0.0313,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9597,0.0605,0.0034,0.0000</t>
+  </si>
+  <si>
+    <t>0.9446,0.0033,0.0356,0.0000</t>
   </si>
   <si>
     <t>0.9765,0.0143,0.0042,0.0000</t>
@@ -1177,28 +1186,28 @@
     <t>0.9806,0.0064,0.0055,0.0000</t>
   </si>
   <si>
-    <t>0.3780,0.2704,0.1489,0.0304</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0191,0.0000</t>
+    <t>0.3778,0.2698,0.1492,0.0305</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0192,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0062,0.0000</t>
   </si>
   <si>
-    <t>0.0264,0.9891,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.1192,0.0000</t>
-  </si>
-  <si>
-    <t>0.3078,0.8621,0.0033,0.0000</t>
-  </si>
-  <si>
-    <t>0.9851,0.0506,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9442,0.2106,0.0005,0.0000</t>
+    <t>0.0265,0.9891,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.1194,0.0000</t>
+  </si>
+  <si>
+    <t>0.3081,0.8618,0.0033,0.0000</t>
+  </si>
+  <si>
+    <t>0.9851,0.0505,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9443,0.2101,0.0005,0.0000</t>
   </si>
   <si>
     <t>0.9995,0.0009,0.0001,0.0000</t>
@@ -1219,28 +1228,28 @@
     <t>0.9993,0.0008,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9978,0.0029,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0027,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0092,0.8967,0.7597,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.5301,0.9741,0.0000</t>
-  </si>
-  <si>
-    <t>0.0038,0.1563,0.9907,0.0001</t>
-  </si>
-  <si>
-    <t>0.2101,0.0608,0.7762,0.0001</t>
+    <t>0.9979,0.0029,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0026,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0092,0.8965,0.7600,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.5291,0.9742,0.0000</t>
+  </si>
+  <si>
+    <t>0.0038,0.1559,0.9907,0.0001</t>
+  </si>
+  <si>
+    <t>0.2101,0.0606,0.7766,0.0001</t>
   </si>
   <si>
     <t>0.9985,0.0008,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.9739,0.0454,0.0020,0.0000</t>
+    <t>0.9740,0.0453,0.0020,0.0000</t>
   </si>
   <si>
     <t>0.9693,0.0001,0.0296,0.0000</t>
@@ -1252,40 +1261,40 @@
     <t>0.9820,0.0022,0.0005,0.0012</t>
   </si>
   <si>
-    <t>0.0235,0.0133,0.0007,0.9711</t>
-  </si>
-  <si>
-    <t>0.1668,0.0022,0.0003,0.8627</t>
+    <t>0.0235,0.0133,0.0007,0.9712</t>
+  </si>
+  <si>
+    <t>0.1667,0.0022,0.0003,0.8630</t>
   </si>
   <si>
     <t>0.9158,0.0024,0.0002,0.0080</t>
   </si>
   <si>
-    <t>0.0012,0.9868,0.7845,0.0001</t>
+    <t>0.0012,0.9867,0.7847,0.0001</t>
   </si>
   <si>
     <t>0.9958,0.0064,0.0007,0.0000</t>
   </si>
   <si>
-    <t>0.6941,0.6020,0.0023,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0049,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8298,0.4207,0.0013,0.0000</t>
+    <t>0.6945,0.6014,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0048,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.8301,0.4199,0.0013,0.0000</t>
   </si>
   <si>
     <t>0.9989,0.0019,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.8904,0.0002,0.1127,0.0000</t>
-  </si>
-  <si>
-    <t>0.9493,0.0027,0.0383,0.0000</t>
-  </si>
-  <si>
-    <t>0.2369,0.0000,0.8171,0.0000</t>
+    <t>0.8902,0.0002,0.1129,0.0000</t>
+  </si>
+  <si>
+    <t>0.9492,0.0027,0.0384,0.0000</t>
+  </si>
+  <si>
+    <t>0.2367,0.0000,0.8173,0.0000</t>
   </si>
   <si>
     <t>0.9957,0.0024,0.0017,0.0000</t>
@@ -1294,7 +1303,7 @@
     <t>0.9921,0.0194,0.0007,0.0000</t>
   </si>
   <si>
-    <t>0.9667,0.0880,0.0012,0.0000</t>
+    <t>0.9668,0.0878,0.0012,0.0000</t>
   </si>
   <si>
     <t>0.9984,0.0029,0.0002,0.0000</t>
@@ -1303,7 +1312,7 @@
     <t>0.9976,0.0035,0.0004,0.0000</t>
   </si>
   <si>
-    <t>0.9197,0.2297,0.0014,0.0000</t>
+    <t>0.9199,0.2292,0.0014,0.0000</t>
   </si>
   <si>
     <t>0.9971,0.0070,0.0003,0.0000</t>
@@ -1321,7 +1330,7 @@
     <t>0.9977,0.0043,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.9906,0.0178,0.0013,0.0000</t>
+    <t>0.9906,0.0177,0.0013,0.0000</t>
   </si>
   <si>
     <t>0.9985,0.0034,0.0002,0.0000</t>
@@ -1336,22 +1345,22 @@
     <t>0.9906,0.0192,0.0010,0.0000</t>
   </si>
   <si>
-    <t>0.9693,0.1241,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9738,0.1044,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9496,0.1668,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.9861,0.0164,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.9875,0.0331,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9765,0.0461,0.0014,0.0000</t>
+    <t>0.9694,0.1237,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9738,0.1041,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9497,0.1664,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9861,0.0163,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.9875,0.0330,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9766,0.0460,0.0014,0.0000</t>
   </si>
   <si>
     <t>0.9932,0.0131,0.0009,0.0000</t>
@@ -1360,103 +1369,103 @@
     <t>0.9952,0.0133,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.7019,0.0764,0.0594,0.0001</t>
-  </si>
-  <si>
-    <t>0.9650,0.0684,0.0018,0.0000</t>
-  </si>
-  <si>
-    <t>0.0850,0.0021,0.9465,0.0000</t>
-  </si>
-  <si>
-    <t>0.0582,0.0395,0.9425,0.0006</t>
-  </si>
-  <si>
-    <t>0.9369,0.0183,0.0251,0.0001</t>
-  </si>
-  <si>
-    <t>0.0835,0.2779,0.6626,0.0001</t>
-  </si>
-  <si>
-    <t>0.2723,0.0097,0.7103,0.0000</t>
-  </si>
-  <si>
-    <t>0.7107,0.0001,0.5005,0.0000</t>
-  </si>
-  <si>
-    <t>0.8794,0.0006,0.1581,0.0000</t>
-  </si>
-  <si>
-    <t>0.9274,0.0112,0.0275,0.0000</t>
+    <t>0.7020,0.0761,0.0595,0.0001</t>
+  </si>
+  <si>
+    <t>0.9650,0.0683,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0848,0.0021,0.9466,0.0000</t>
+  </si>
+  <si>
+    <t>0.0581,0.0393,0.9427,0.0006</t>
+  </si>
+  <si>
+    <t>0.9369,0.0182,0.0251,0.0001</t>
+  </si>
+  <si>
+    <t>0.0836,0.2771,0.6632,0.0001</t>
+  </si>
+  <si>
+    <t>0.2720,0.0096,0.7110,0.0000</t>
+  </si>
+  <si>
+    <t>0.7104,0.0001,0.5010,0.0000</t>
+  </si>
+  <si>
+    <t>0.8793,0.0006,0.1584,0.0000</t>
+  </si>
+  <si>
+    <t>0.9273,0.0111,0.0275,0.0000</t>
   </si>
   <si>
     <t>0.9758,0.0011,0.0138,0.0000</t>
   </si>
   <si>
-    <t>0.9655,0.0428,0.0038,0.0000</t>
-  </si>
-  <si>
-    <t>0.9305,0.0168,0.0209,0.0000</t>
-  </si>
-  <si>
-    <t>0.9202,0.0291,0.0143,0.0000</t>
-  </si>
-  <si>
-    <t>0.9189,0.0052,0.0493,0.0000</t>
+    <t>0.9656,0.0427,0.0038,0.0000</t>
+  </si>
+  <si>
+    <t>0.9305,0.0167,0.0209,0.0000</t>
+  </si>
+  <si>
+    <t>0.9203,0.0290,0.0143,0.0000</t>
+  </si>
+  <si>
+    <t>0.9188,0.0052,0.0494,0.0000</t>
   </si>
   <si>
     <t>0.9652,0.0177,0.0071,0.0000</t>
   </si>
   <si>
-    <t>0.9524,0.0313,0.0095,0.0000</t>
-  </si>
-  <si>
-    <t>0.9565,0.1515,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.7970,0.5365,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9409,0.2057,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9697,0.0635,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9737,0.0627,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9333,0.1714,0.0013,0.0000</t>
+    <t>0.9524,0.0312,0.0096,0.0000</t>
+  </si>
+  <si>
+    <t>0.9566,0.1512,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.7973,0.5359,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9410,0.2053,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9697,0.0634,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9737,0.0626,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.9334,0.1709,0.0013,0.0000</t>
   </si>
   <si>
     <t>0.9991,0.0005,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.9718,0.0157,0.0064,0.0000</t>
-  </si>
-  <si>
-    <t>0.9447,0.0033,0.0329,0.0000</t>
+    <t>0.9718,0.0156,0.0064,0.0000</t>
+  </si>
+  <si>
+    <t>0.9446,0.0033,0.0330,0.0000</t>
   </si>
   <si>
     <t>0.9940,0.0022,0.0013,0.0000</t>
   </si>
   <si>
-    <t>0.8498,0.0025,0.1161,0.0000</t>
-  </si>
-  <si>
-    <t>0.3837,0.0398,0.5060,0.0002</t>
-  </si>
-  <si>
-    <t>0.7238,0.0311,0.1398,0.0001</t>
-  </si>
-  <si>
-    <t>0.0701,0.0727,0.9403,0.0005</t>
-  </si>
-  <si>
-    <t>0.2459,0.0633,0.5763,0.0001</t>
-  </si>
-  <si>
-    <t>0.9839,0.0297,0.0018,0.0000</t>
+    <t>0.8496,0.0025,0.1164,0.0000</t>
+  </si>
+  <si>
+    <t>0.3834,0.0396,0.5067,0.0002</t>
+  </si>
+  <si>
+    <t>0.7237,0.0310,0.1403,0.0001</t>
+  </si>
+  <si>
+    <t>0.0701,0.0723,0.9404,0.0005</t>
+  </si>
+  <si>
+    <t>0.2459,0.0629,0.5773,0.0001</t>
+  </si>
+  <si>
+    <t>0.9839,0.0297,0.0019,0.0000</t>
   </si>
   <si>
     <t>0.9950,0.0119,0.0004,0.0000</t>
@@ -1471,7 +1480,7 @@
     <t>0.9971,0.0064,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.9958,0.0100,0.0003,0.0000</t>
+    <t>0.9959,0.0100,0.0003,0.0000</t>
   </si>
   <si>
     <t>0.9961,0.0095,0.0003,0.0000</t>
@@ -1480,13 +1489,13 @@
     <t>0.9875,0.0233,0.0016,0.0000</t>
   </si>
   <si>
-    <t>0.9603,0.0040,0.0224,0.0000</t>
-  </si>
-  <si>
-    <t>0.9638,0.0254,0.0053,0.0000</t>
-  </si>
-  <si>
-    <t>0.9922,0.0051,0.0020,0.0000</t>
+    <t>0.9603,0.0040,0.0225,0.0000</t>
+  </si>
+  <si>
+    <t>0.9638,0.0253,0.0053,0.0000</t>
+  </si>
+  <si>
+    <t>0.9922,0.0050,0.0020,0.0000</t>
   </si>
   <si>
     <t>0.0188,0.0009,0.9903,0.0000</t>
@@ -1495,22 +1504,22 @@
     <t>0.0067,0.0052,0.9950,0.0001</t>
   </si>
   <si>
-    <t>0.5128,0.0119,0.4810,0.0001</t>
+    <t>0.5126,0.0119,0.4817,0.0001</t>
   </si>
   <si>
     <t>0.0016,0.0001,0.9991,0.0000</t>
   </si>
   <si>
-    <t>0.7184,0.0062,0.3198,0.0001</t>
+    <t>0.7183,0.0062,0.3202,0.0001</t>
   </si>
   <si>
     <t>0.0005,0.0000,0.9998,0.0000</t>
   </si>
   <si>
-    <t>0.0695,0.0054,0.9651,0.0001</t>
-  </si>
-  <si>
-    <t>0.9139,0.0322,0.0231,0.0001</t>
+    <t>0.0694,0.0054,0.9652,0.0001</t>
+  </si>
+  <si>
+    <t>0.9139,0.0321,0.0231,0.0001</t>
   </si>
   <si>
     <t>0.9901,0.0013,0.0027,0.0000</t>
@@ -1522,7 +1531,7 @@
     <t>0.9983,0.0019,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.9607,0.0980,0.0014,0.0000</t>
+    <t>0.9607,0.0978,0.0014,0.0000</t>
   </si>
   <si>
     <t>0.9944,0.0189,0.0003,0.0000</t>
@@ -1534,7 +1543,7 @@
     <t>0.9926,0.0163,0.0006,0.0000</t>
   </si>
   <si>
-    <t>0.9746,0.0527,0.0018,0.0000</t>
+    <t>0.9746,0.0526,0.0018,0.0000</t>
   </si>
   <si>
     <t>0.9904,0.0259,0.0004,0.0000</t>
@@ -1546,43 +1555,43 @@
     <t>0.9956,0.0081,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.3549,0.0574,0.5042,0.0002</t>
-  </si>
-  <si>
-    <t>0.1387,0.0293,0.8925,0.0001</t>
-  </si>
-  <si>
-    <t>0.1551,0.0156,0.8937,0.0001</t>
-  </si>
-  <si>
-    <t>0.8312,0.0095,0.1149,0.0001</t>
-  </si>
-  <si>
-    <t>0.8315,0.0002,0.3069,0.0000</t>
-  </si>
-  <si>
-    <t>0.8989,0.1645,0.0100,0.0006</t>
-  </si>
-  <si>
-    <t>0.8973,0.0839,0.0186,0.0002</t>
-  </si>
-  <si>
-    <t>0.0549,0.0018,0.9564,0.0019</t>
+    <t>0.3551,0.0571,0.5050,0.0002</t>
+  </si>
+  <si>
+    <t>0.1386,0.0292,0.8928,0.0001</t>
+  </si>
+  <si>
+    <t>0.1549,0.0155,0.8939,0.0001</t>
+  </si>
+  <si>
+    <t>0.8311,0.0094,0.1151,0.0001</t>
+  </si>
+  <si>
+    <t>0.8313,0.0002,0.3074,0.0000</t>
+  </si>
+  <si>
+    <t>0.8990,0.1641,0.0100,0.0006</t>
+  </si>
+  <si>
+    <t>0.8974,0.0836,0.0186,0.0002</t>
+  </si>
+  <si>
+    <t>0.0549,0.0018,0.9565,0.0019</t>
   </si>
   <si>
     <t>0.9988,0.0007,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.7913,0.0023,0.0003,0.0578</t>
+    <t>0.7913,0.0023,0.0003,0.0579</t>
   </si>
   <si>
     <t>0.9549,0.0048,0.0008,0.0045</t>
   </si>
   <si>
-    <t>0.0563,0.0006,0.0090,0.9685</t>
-  </si>
-  <si>
-    <t>0.2300,0.0012,0.0005,0.8300</t>
+    <t>0.0562,0.0006,0.0091,0.9686</t>
+  </si>
+  <si>
+    <t>0.2298,0.0012,0.0005,0.8306</t>
   </si>
   <si>
     <t>0.9962,0.0031,0.0004,0.0000</t>
@@ -1971,7 +1980,7 @@
         <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1985,7 +1994,7 @@
         <v>264</v>
       </c>
       <c r="D3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1999,7 +2008,7 @@
         <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2013,7 +2022,7 @@
         <v>264</v>
       </c>
       <c r="D5" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2027,7 +2036,7 @@
         <v>264</v>
       </c>
       <c r="D6" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2041,7 +2050,7 @@
         <v>264</v>
       </c>
       <c r="D7" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2055,7 +2064,7 @@
         <v>264</v>
       </c>
       <c r="D8" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2069,7 +2078,7 @@
         <v>264</v>
       </c>
       <c r="D9" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2083,7 +2092,7 @@
         <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2097,7 +2106,7 @@
         <v>264</v>
       </c>
       <c r="D11" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2111,7 +2120,7 @@
         <v>264</v>
       </c>
       <c r="D12" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2125,7 +2134,7 @@
         <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2139,7 +2148,7 @@
         <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2153,7 +2162,7 @@
         <v>264</v>
       </c>
       <c r="D15" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2167,7 +2176,7 @@
         <v>264</v>
       </c>
       <c r="D16" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2181,7 +2190,7 @@
         <v>264</v>
       </c>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2195,7 +2204,7 @@
         <v>264</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2209,7 +2218,7 @@
         <v>265</v>
       </c>
       <c r="D19" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2223,7 +2232,7 @@
         <v>265</v>
       </c>
       <c r="D20" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2234,10 +2243,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D21" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2251,7 +2260,7 @@
         <v>265</v>
       </c>
       <c r="D22" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2265,7 +2274,7 @@
         <v>265</v>
       </c>
       <c r="D23" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2279,7 +2288,7 @@
         <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2293,7 +2302,7 @@
         <v>264</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2307,7 +2316,7 @@
         <v>264</v>
       </c>
       <c r="D26" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2321,7 +2330,7 @@
         <v>264</v>
       </c>
       <c r="D27" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2335,7 +2344,7 @@
         <v>264</v>
       </c>
       <c r="D28" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2349,7 +2358,7 @@
         <v>264</v>
       </c>
       <c r="D29" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2360,10 +2369,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D30" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2377,7 +2386,7 @@
         <v>264</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2391,7 +2400,7 @@
         <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2405,7 +2414,7 @@
         <v>264</v>
       </c>
       <c r="D33" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2419,7 +2428,7 @@
         <v>264</v>
       </c>
       <c r="D34" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2433,7 +2442,7 @@
         <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2447,7 +2456,7 @@
         <v>264</v>
       </c>
       <c r="D36" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2461,7 +2470,7 @@
         <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2475,7 +2484,7 @@
         <v>264</v>
       </c>
       <c r="D38" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2486,10 +2495,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D39" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2500,10 +2509,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D40" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2514,10 +2523,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2531,7 +2540,7 @@
         <v>264</v>
       </c>
       <c r="D42" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2542,10 +2551,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D43" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2559,7 +2568,7 @@
         <v>265</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2570,10 +2579,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D45" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2587,7 +2596,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2601,7 +2610,7 @@
         <v>265</v>
       </c>
       <c r="D47" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2615,7 +2624,7 @@
         <v>265</v>
       </c>
       <c r="D48" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2629,7 +2638,7 @@
         <v>265</v>
       </c>
       <c r="D49" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2640,10 +2649,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D50" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2654,10 +2663,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D51" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2668,10 +2677,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D52" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2685,7 +2694,7 @@
         <v>264</v>
       </c>
       <c r="D53" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2699,7 +2708,7 @@
         <v>264</v>
       </c>
       <c r="D54" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2713,7 +2722,7 @@
         <v>264</v>
       </c>
       <c r="D55" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2727,7 +2736,7 @@
         <v>264</v>
       </c>
       <c r="D56" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2741,7 +2750,7 @@
         <v>264</v>
       </c>
       <c r="D57" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2755,7 +2764,7 @@
         <v>264</v>
       </c>
       <c r="D58" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2769,7 +2778,7 @@
         <v>264</v>
       </c>
       <c r="D59" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2783,7 +2792,7 @@
         <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2797,7 +2806,7 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2811,7 +2820,7 @@
         <v>264</v>
       </c>
       <c r="D62" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2822,10 +2831,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D63" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2836,10 +2845,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D64" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2850,10 +2859,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D65" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2864,10 +2873,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D66" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2878,10 +2887,10 @@
         <v>261</v>
       </c>
       <c r="C67" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D67" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2895,7 +2904,7 @@
         <v>265</v>
       </c>
       <c r="D68" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2909,7 +2918,7 @@
         <v>265</v>
       </c>
       <c r="D69" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2923,7 +2932,7 @@
         <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2937,7 +2946,7 @@
         <v>264</v>
       </c>
       <c r="D71" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2951,7 +2960,7 @@
         <v>264</v>
       </c>
       <c r="D72" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2962,10 +2971,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D73" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2976,10 +2985,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D74" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2990,10 +2999,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D75" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3004,10 +3013,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D76" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3021,7 +3030,7 @@
         <v>264</v>
       </c>
       <c r="D77" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3035,7 +3044,7 @@
         <v>264</v>
       </c>
       <c r="D78" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3049,7 +3058,7 @@
         <v>264</v>
       </c>
       <c r="D79" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3063,7 +3072,7 @@
         <v>264</v>
       </c>
       <c r="D80" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3077,7 +3086,7 @@
         <v>264</v>
       </c>
       <c r="D81" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3088,10 +3097,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D82" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3102,10 +3111,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D83" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3116,10 +3125,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D84" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3130,10 +3139,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D85" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3144,10 +3153,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D86" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3158,10 +3167,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D87" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3175,7 +3184,7 @@
         <v>265</v>
       </c>
       <c r="D88" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3189,7 +3198,7 @@
         <v>264</v>
       </c>
       <c r="D89" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3203,7 +3212,7 @@
         <v>264</v>
       </c>
       <c r="D90" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3217,7 +3226,7 @@
         <v>264</v>
       </c>
       <c r="D91" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3231,7 +3240,7 @@
         <v>264</v>
       </c>
       <c r="D92" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3245,7 +3254,7 @@
         <v>264</v>
       </c>
       <c r="D93" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3259,7 +3268,7 @@
         <v>264</v>
       </c>
       <c r="D94" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3273,7 +3282,7 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3287,7 +3296,7 @@
         <v>264</v>
       </c>
       <c r="D96" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3301,7 +3310,7 @@
         <v>264</v>
       </c>
       <c r="D97" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3315,7 +3324,7 @@
         <v>264</v>
       </c>
       <c r="D98" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3329,7 +3338,7 @@
         <v>264</v>
       </c>
       <c r="D99" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3343,7 +3352,7 @@
         <v>264</v>
       </c>
       <c r="D100" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3357,7 +3366,7 @@
         <v>264</v>
       </c>
       <c r="D101" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3371,7 +3380,7 @@
         <v>264</v>
       </c>
       <c r="D102" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3385,7 +3394,7 @@
         <v>264</v>
       </c>
       <c r="D103" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3399,7 +3408,7 @@
         <v>264</v>
       </c>
       <c r="D104" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3410,10 +3419,10 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D105" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3427,7 +3436,7 @@
         <v>264</v>
       </c>
       <c r="D106" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3441,7 +3450,7 @@
         <v>264</v>
       </c>
       <c r="D107" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3455,7 +3464,7 @@
         <v>264</v>
       </c>
       <c r="D108" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3469,7 +3478,7 @@
         <v>265</v>
       </c>
       <c r="D109" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3483,7 +3492,7 @@
         <v>265</v>
       </c>
       <c r="D110" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3494,10 +3503,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D111" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3508,10 +3517,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D112" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3525,7 +3534,7 @@
         <v>265</v>
       </c>
       <c r="D113" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3539,7 +3548,7 @@
         <v>265</v>
       </c>
       <c r="D114" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3553,7 +3562,7 @@
         <v>264</v>
       </c>
       <c r="D115" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3567,7 +3576,7 @@
         <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3581,7 +3590,7 @@
         <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3595,7 +3604,7 @@
         <v>264</v>
       </c>
       <c r="D118" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3609,7 +3618,7 @@
         <v>264</v>
       </c>
       <c r="D119" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3620,10 +3629,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3637,7 +3646,7 @@
         <v>265</v>
       </c>
       <c r="D121" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3651,7 +3660,7 @@
         <v>265</v>
       </c>
       <c r="D122" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3665,7 +3674,7 @@
         <v>265</v>
       </c>
       <c r="D123" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3679,7 +3688,7 @@
         <v>265</v>
       </c>
       <c r="D124" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3693,7 +3702,7 @@
         <v>265</v>
       </c>
       <c r="D125" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3707,7 +3716,7 @@
         <v>264</v>
       </c>
       <c r="D126" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3721,7 +3730,7 @@
         <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3735,7 +3744,7 @@
         <v>264</v>
       </c>
       <c r="D128" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3749,7 +3758,7 @@
         <v>264</v>
       </c>
       <c r="D129" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3763,7 +3772,7 @@
         <v>264</v>
       </c>
       <c r="D130" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3777,7 +3786,7 @@
         <v>264</v>
       </c>
       <c r="D131" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3791,7 +3800,7 @@
         <v>264</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3805,7 +3814,7 @@
         <v>264</v>
       </c>
       <c r="D133" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3819,7 +3828,7 @@
         <v>264</v>
       </c>
       <c r="D134" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3833,7 +3842,7 @@
         <v>264</v>
       </c>
       <c r="D135" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3844,10 +3853,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D136" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3858,10 +3867,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D137" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3872,10 +3881,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D138" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3886,10 +3895,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D139" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3903,7 +3912,7 @@
         <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3917,7 +3926,7 @@
         <v>264</v>
       </c>
       <c r="D141" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3931,7 +3940,7 @@
         <v>264</v>
       </c>
       <c r="D142" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3945,7 +3954,7 @@
         <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3959,7 +3968,7 @@
         <v>264</v>
       </c>
       <c r="D144" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3970,10 +3979,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D145" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3984,10 +3993,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D146" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4001,7 +4010,7 @@
         <v>264</v>
       </c>
       <c r="D147" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4012,10 +4021,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D148" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4029,7 +4038,7 @@
         <v>264</v>
       </c>
       <c r="D149" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4040,10 +4049,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D150" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4057,7 +4066,7 @@
         <v>264</v>
       </c>
       <c r="D151" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4071,7 +4080,7 @@
         <v>264</v>
       </c>
       <c r="D152" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4085,7 +4094,7 @@
         <v>264</v>
       </c>
       <c r="D153" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4099,7 +4108,7 @@
         <v>264</v>
       </c>
       <c r="D154" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4113,7 +4122,7 @@
         <v>264</v>
       </c>
       <c r="D155" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4124,10 +4133,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D156" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4141,7 +4150,7 @@
         <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4155,7 +4164,7 @@
         <v>264</v>
       </c>
       <c r="D158" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4169,7 +4178,7 @@
         <v>264</v>
       </c>
       <c r="D159" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4183,7 +4192,7 @@
         <v>264</v>
       </c>
       <c r="D160" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4197,7 +4206,7 @@
         <v>264</v>
       </c>
       <c r="D161" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4211,7 +4220,7 @@
         <v>264</v>
       </c>
       <c r="D162" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4225,7 +4234,7 @@
         <v>264</v>
       </c>
       <c r="D163" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4239,7 +4248,7 @@
         <v>264</v>
       </c>
       <c r="D164" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4253,7 +4262,7 @@
         <v>264</v>
       </c>
       <c r="D165" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4267,7 +4276,7 @@
         <v>264</v>
       </c>
       <c r="D166" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4281,7 +4290,7 @@
         <v>264</v>
       </c>
       <c r="D167" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4295,7 +4304,7 @@
         <v>264</v>
       </c>
       <c r="D168" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4309,7 +4318,7 @@
         <v>264</v>
       </c>
       <c r="D169" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4323,7 +4332,7 @@
         <v>264</v>
       </c>
       <c r="D170" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4337,7 +4346,7 @@
         <v>264</v>
       </c>
       <c r="D171" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4351,7 +4360,7 @@
         <v>264</v>
       </c>
       <c r="D172" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4365,7 +4374,7 @@
         <v>264</v>
       </c>
       <c r="D173" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4379,7 +4388,7 @@
         <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4393,7 +4402,7 @@
         <v>264</v>
       </c>
       <c r="D175" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4407,7 +4416,7 @@
         <v>264</v>
       </c>
       <c r="D176" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4421,7 +4430,7 @@
         <v>264</v>
       </c>
       <c r="D177" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4435,7 +4444,7 @@
         <v>264</v>
       </c>
       <c r="D178" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4449,7 +4458,7 @@
         <v>264</v>
       </c>
       <c r="D179" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4463,7 +4472,7 @@
         <v>264</v>
       </c>
       <c r="D180" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4477,7 +4486,7 @@
         <v>264</v>
       </c>
       <c r="D181" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4491,7 +4500,7 @@
         <v>264</v>
       </c>
       <c r="D182" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4502,10 +4511,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D183" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4516,10 +4525,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D184" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4533,7 +4542,7 @@
         <v>264</v>
       </c>
       <c r="D185" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4544,10 +4553,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D186" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4558,10 +4567,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D187" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4572,10 +4581,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D188" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4589,7 +4598,7 @@
         <v>264</v>
       </c>
       <c r="D189" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4603,7 +4612,7 @@
         <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4617,7 +4626,7 @@
         <v>264</v>
       </c>
       <c r="D191" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4631,7 +4640,7 @@
         <v>264</v>
       </c>
       <c r="D192" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4645,7 +4654,7 @@
         <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4659,7 +4668,7 @@
         <v>264</v>
       </c>
       <c r="D194" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4673,7 +4682,7 @@
         <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4687,7 +4696,7 @@
         <v>264</v>
       </c>
       <c r="D196" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4701,7 +4710,7 @@
         <v>264</v>
       </c>
       <c r="D197" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4715,7 +4724,7 @@
         <v>264</v>
       </c>
       <c r="D198" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4726,10 +4735,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D199" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4743,7 +4752,7 @@
         <v>264</v>
       </c>
       <c r="D200" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4757,7 +4766,7 @@
         <v>264</v>
       </c>
       <c r="D201" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4771,7 +4780,7 @@
         <v>264</v>
       </c>
       <c r="D202" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4785,7 +4794,7 @@
         <v>264</v>
       </c>
       <c r="D203" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4799,7 +4808,7 @@
         <v>264</v>
       </c>
       <c r="D204" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4813,7 +4822,7 @@
         <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4827,7 +4836,7 @@
         <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4841,7 +4850,7 @@
         <v>264</v>
       </c>
       <c r="D207" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4855,7 +4864,7 @@
         <v>264</v>
       </c>
       <c r="D208" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4866,10 +4875,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D209" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4883,7 +4892,7 @@
         <v>264</v>
       </c>
       <c r="D210" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4894,10 +4903,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D211" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4908,10 +4917,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D212" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4925,7 +4934,7 @@
         <v>264</v>
       </c>
       <c r="D213" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4939,7 +4948,7 @@
         <v>264</v>
       </c>
       <c r="D214" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4953,7 +4962,7 @@
         <v>264</v>
       </c>
       <c r="D215" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4967,7 +4976,7 @@
         <v>264</v>
       </c>
       <c r="D216" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4981,7 +4990,7 @@
         <v>264</v>
       </c>
       <c r="D217" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4995,7 +5004,7 @@
         <v>264</v>
       </c>
       <c r="D218" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5009,7 +5018,7 @@
         <v>264</v>
       </c>
       <c r="D219" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5023,7 +5032,7 @@
         <v>264</v>
       </c>
       <c r="D220" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5037,7 +5046,7 @@
         <v>264</v>
       </c>
       <c r="D221" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5051,7 +5060,7 @@
         <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5065,7 +5074,7 @@
         <v>264</v>
       </c>
       <c r="D223" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5076,10 +5085,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D224" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5090,10 +5099,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D225" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5107,7 +5116,7 @@
         <v>264</v>
       </c>
       <c r="D226" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5118,10 +5127,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D227" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5135,7 +5144,7 @@
         <v>264</v>
       </c>
       <c r="D228" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5146,10 +5155,10 @@
         <v>261</v>
       </c>
       <c r="C229" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D229" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5160,10 +5169,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D230" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5177,7 +5186,7 @@
         <v>264</v>
       </c>
       <c r="D231" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5191,7 +5200,7 @@
         <v>264</v>
       </c>
       <c r="D232" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5205,7 +5214,7 @@
         <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5219,7 +5228,7 @@
         <v>264</v>
       </c>
       <c r="D234" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5233,7 +5242,7 @@
         <v>264</v>
       </c>
       <c r="D235" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5247,7 +5256,7 @@
         <v>264</v>
       </c>
       <c r="D236" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5261,7 +5270,7 @@
         <v>264</v>
       </c>
       <c r="D237" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5275,7 +5284,7 @@
         <v>264</v>
       </c>
       <c r="D238" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5289,7 +5298,7 @@
         <v>264</v>
       </c>
       <c r="D239" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5303,7 +5312,7 @@
         <v>264</v>
       </c>
       <c r="D240" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5317,7 +5326,7 @@
         <v>264</v>
       </c>
       <c r="D241" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5331,7 +5340,7 @@
         <v>264</v>
       </c>
       <c r="D242" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5342,10 +5351,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D243" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5356,10 +5365,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D244" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5370,10 +5379,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D245" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5387,7 +5396,7 @@
         <v>264</v>
       </c>
       <c r="D246" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5401,7 +5410,7 @@
         <v>264</v>
       </c>
       <c r="D247" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5415,7 +5424,7 @@
         <v>264</v>
       </c>
       <c r="D248" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5429,7 +5438,7 @@
         <v>264</v>
       </c>
       <c r="D249" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5440,10 +5449,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D250" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5457,7 +5466,7 @@
         <v>264</v>
       </c>
       <c r="D251" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5471,7 +5480,7 @@
         <v>264</v>
       </c>
       <c r="D252" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5485,7 +5494,7 @@
         <v>264</v>
       </c>
       <c r="D253" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5496,10 +5505,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D254" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5510,10 +5519,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D255" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5527,7 +5536,7 @@
         <v>264</v>
       </c>
       <c r="D256" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
   </sheetData>
